--- a/data/base/Backlog_49.xlsx
+++ b/data/base/Backlog_49.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\netuno\Departamentos\GTI\Governança de TI\Governança Adriano\Backlog\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\franciscoj\Python_Initial\Pyhton_Web\data\base\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{362C8D01-3F13-42B1-ADE7-A0C1273A0DBA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63155585-FBB1-44D9-88CE-08FA7EF07304}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="273" xr2:uid="{89A3EF9E-2AF9-420D-85DF-9BB5B68F651F}"/>
   </bookViews>
@@ -18,7 +18,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">ITI!$A$1:$K$20</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">SPN!$A$1:$J$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">SPN!$A$1:$K$2</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
   <extLst>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="30">
   <si>
     <t>Setor</t>
   </si>
@@ -128,6 +128,9 @@
   </si>
   <si>
     <t>Mara Moraes</t>
+  </si>
+  <si>
+    <t>Resolvido</t>
   </si>
 </sst>
 </file>
@@ -576,7 +579,7 @@
   <sheetFormatPr defaultColWidth="9.5703125" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.85546875" style="11" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="22.5703125" style="5" customWidth="1"/>
+    <col min="2" max="2" width="16.85546875" style="5" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="13" style="11" customWidth="1"/>
     <col min="4" max="4" width="13.28515625" style="11" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="19.85546875" style="11" bestFit="1" customWidth="1"/>
@@ -629,7 +632,7 @@
         <v>11</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C2" s="9">
         <v>2025</v>
@@ -644,7 +647,7 @@
         <v>46003</v>
       </c>
       <c r="G2" s="1">
-        <v>5448</v>
+        <v>5581</v>
       </c>
       <c r="H2" s="3">
         <v>45962</v>
@@ -664,7 +667,7 @@
         <v>11</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="C3" s="9">
         <v>2025</v>
@@ -679,7 +682,7 @@
         <v>46003</v>
       </c>
       <c r="G3" s="1">
-        <v>5581</v>
+        <v>6016</v>
       </c>
       <c r="H3" s="3">
         <v>45962</v>
@@ -699,7 +702,7 @@
         <v>11</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="C4" s="9">
         <v>2025</v>
@@ -714,7 +717,7 @@
         <v>46003</v>
       </c>
       <c r="G4" s="1">
-        <v>5650</v>
+        <v>6281</v>
       </c>
       <c r="H4" s="3">
         <v>45962</v>
@@ -734,7 +737,7 @@
         <v>11</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C5" s="9">
         <v>2025</v>
@@ -749,16 +752,16 @@
         <v>46003</v>
       </c>
       <c r="G5" s="1">
-        <v>5828</v>
+        <v>6923</v>
       </c>
       <c r="H5" s="3">
-        <v>45962</v>
+        <v>45992</v>
       </c>
       <c r="I5" s="2">
         <v>45999</v>
       </c>
       <c r="J5" s="9" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="K5" s="9" t="s">
         <v>13</v>
@@ -769,7 +772,7 @@
         <v>11</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="C6" s="9">
         <v>2025</v>
@@ -784,16 +787,16 @@
         <v>46003</v>
       </c>
       <c r="G6" s="1">
-        <v>6015</v>
+        <v>6961</v>
       </c>
       <c r="H6" s="3">
-        <v>45962</v>
+        <v>45992</v>
       </c>
       <c r="I6" s="2">
         <v>45999</v>
       </c>
       <c r="J6" s="9" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="K6" s="9" t="s">
         <v>13</v>
@@ -804,7 +807,7 @@
         <v>11</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C7" s="9">
         <v>2025</v>
@@ -819,16 +822,16 @@
         <v>46003</v>
       </c>
       <c r="G7" s="1">
-        <v>6016</v>
+        <v>6726</v>
       </c>
       <c r="H7" s="3">
-        <v>45962</v>
+        <v>45992</v>
       </c>
       <c r="I7" s="2">
         <v>45999</v>
       </c>
       <c r="J7" s="9" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="K7" s="9" t="s">
         <v>13</v>
@@ -839,7 +842,7 @@
         <v>11</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="C8" s="9">
         <v>2025</v>
@@ -854,7 +857,7 @@
         <v>46003</v>
       </c>
       <c r="G8" s="1">
-        <v>6281</v>
+        <v>5650</v>
       </c>
       <c r="H8" s="3">
         <v>45962</v>
@@ -863,7 +866,7 @@
         <v>45999</v>
       </c>
       <c r="J8" s="9" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="K8" s="9" t="s">
         <v>13</v>
@@ -874,7 +877,7 @@
         <v>11</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="C9" s="9">
         <v>2025</v>
@@ -889,16 +892,16 @@
         <v>46003</v>
       </c>
       <c r="G9" s="1">
-        <v>6367</v>
+        <v>6515</v>
       </c>
       <c r="H9" s="3">
-        <v>45962</v>
+        <v>45992</v>
       </c>
       <c r="I9" s="2">
         <v>45999</v>
       </c>
       <c r="J9" s="9" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="K9" s="9" t="s">
         <v>13</v>
@@ -924,7 +927,7 @@
         <v>46003</v>
       </c>
       <c r="G10" s="1">
-        <v>6515</v>
+        <v>7122</v>
       </c>
       <c r="H10" s="3">
         <v>45992</v>
@@ -933,7 +936,7 @@
         <v>45999</v>
       </c>
       <c r="J10" s="9" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="K10" s="9" t="s">
         <v>13</v>
@@ -944,7 +947,7 @@
         <v>11</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C11" s="9">
         <v>2025</v>
@@ -959,16 +962,16 @@
         <v>46003</v>
       </c>
       <c r="G11" s="1">
-        <v>6600</v>
+        <v>5828</v>
       </c>
       <c r="H11" s="3">
-        <v>45992</v>
+        <v>45962</v>
       </c>
       <c r="I11" s="2">
         <v>45999</v>
       </c>
       <c r="J11" s="9" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="K11" s="9" t="s">
         <v>13</v>
@@ -979,7 +982,7 @@
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C12" s="9">
         <v>2025</v>
@@ -994,7 +997,7 @@
         <v>46003</v>
       </c>
       <c r="G12" s="1">
-        <v>6726</v>
+        <v>6994</v>
       </c>
       <c r="H12" s="3">
         <v>45992</v>
@@ -1003,7 +1006,7 @@
         <v>45999</v>
       </c>
       <c r="J12" s="9" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="K12" s="9" t="s">
         <v>13</v>
@@ -1014,7 +1017,7 @@
         <v>11</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="C13" s="9">
         <v>2025</v>
@@ -1029,16 +1032,16 @@
         <v>46003</v>
       </c>
       <c r="G13" s="1">
-        <v>6728</v>
+        <v>5448</v>
       </c>
       <c r="H13" s="3">
-        <v>45992</v>
+        <v>45962</v>
       </c>
       <c r="I13" s="2">
         <v>45999</v>
       </c>
       <c r="J13" s="9" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="K13" s="9" t="s">
         <v>13</v>
@@ -1064,10 +1067,10 @@
         <v>46003</v>
       </c>
       <c r="G14" s="1">
-        <v>6897</v>
+        <v>6015</v>
       </c>
       <c r="H14" s="3">
-        <v>45992</v>
+        <v>45962</v>
       </c>
       <c r="I14" s="2">
         <v>45999</v>
@@ -1084,7 +1087,7 @@
         <v>11</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="C15" s="9">
         <v>2025</v>
@@ -1099,7 +1102,7 @@
         <v>46003</v>
       </c>
       <c r="G15" s="1">
-        <v>6923</v>
+        <v>6897</v>
       </c>
       <c r="H15" s="3">
         <v>45992</v>
@@ -1108,7 +1111,7 @@
         <v>45999</v>
       </c>
       <c r="J15" s="9" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="K15" s="9" t="s">
         <v>13</v>
@@ -1143,7 +1146,7 @@
         <v>45999</v>
       </c>
       <c r="J16" s="9" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="K16" s="9" t="s">
         <v>13</v>
@@ -1189,7 +1192,7 @@
         <v>11</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C18" s="9">
         <v>2025</v>
@@ -1204,16 +1207,16 @@
         <v>46003</v>
       </c>
       <c r="G18" s="1">
-        <v>6961</v>
+        <v>6367</v>
       </c>
       <c r="H18" s="3">
-        <v>45992</v>
+        <v>45962</v>
       </c>
       <c r="I18" s="2">
         <v>45999</v>
       </c>
       <c r="J18" s="9" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="K18" s="9" t="s">
         <v>13</v>
@@ -1224,7 +1227,7 @@
         <v>11</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C19" s="9">
         <v>2025</v>
@@ -1239,7 +1242,7 @@
         <v>46003</v>
       </c>
       <c r="G19" s="1">
-        <v>6994</v>
+        <v>6600</v>
       </c>
       <c r="H19" s="3">
         <v>45992</v>
@@ -1259,7 +1262,7 @@
         <v>11</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="C20" s="9">
         <v>2025</v>
@@ -1274,7 +1277,7 @@
         <v>46003</v>
       </c>
       <c r="G20" s="1">
-        <v>7122</v>
+        <v>6728</v>
       </c>
       <c r="H20" s="3">
         <v>45992</v>
@@ -1283,7 +1286,7 @@
         <v>45999</v>
       </c>
       <c r="J20" s="9" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="K20" s="9" t="s">
         <v>13</v>
@@ -1383,7 +1386,7 @@
         <v>45999</v>
       </c>
       <c r="J2" s="4" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="K2" s="1" t="s">
         <v>16</v>
@@ -1453,7 +1456,7 @@
         <v>45999</v>
       </c>
       <c r="J4" s="4" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="K4" s="1" t="s">
         <v>16</v>
@@ -1488,7 +1491,7 @@
         <v>45999</v>
       </c>
       <c r="J5" s="4" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="K5" s="1" t="s">
         <v>16</v>
@@ -1593,7 +1596,7 @@
         <v>45999</v>
       </c>
       <c r="J8" s="4" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="K8" s="1" t="s">
         <v>16</v>
@@ -1628,13 +1631,14 @@
         <v>45999</v>
       </c>
       <c r="J9" s="4" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="K9" s="1" t="s">
         <v>16</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:K2" xr:uid="{16A6A408-5BF6-4E16-8C71-EC6EB1F5A842}"/>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
